--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Kritina Shrestha</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9849747491</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9849747491</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1095,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9849747491</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9849747491</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1113,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.64397</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.64397</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1172,25 +1166,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.33875</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.33875</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : Iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1291,10 +1281,8 @@
           <t>Kritina Shrestha</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9849747491</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9849747491</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1309,10 +1297,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9849747491</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9849747491</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1329,10 +1315,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.64397</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.64397</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1384,25 +1368,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.33875</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.33875</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -572,10 +572,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -612,23 +612,46 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>IPTV Issue</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -643,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -682,16 +705,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -716,7 +752,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -728,7 +764,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -739,24 +775,24 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1416,6 +1452,214 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 9:15 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379037</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Ameer Chitrakar</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Ameer Chitrakar</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9843909978</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:15:39 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>BKT9843909978</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 11:44:09 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:15:39 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Near Matribhumi School,Madhyapur Thimi 44600 - Bhaktapur Municipality, Bhaktapur, Bagmati, Nepal, Ne</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>ameerchitrakar0@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>08:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>21h 31m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -787,7 +787,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1509,20 +1509,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Ameer Chitrakar</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9843909978</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9843909978</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1612,10 +1606,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1626,7 +1618,7 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,20 +544,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -616,19 +634,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -651,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -666,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -687,6 +706,11 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -700,34 +724,59 @@
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="D3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>2</v>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -741,11 +790,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -787,7 +836,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1652,6 +1701,210 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:09 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>blank display</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379324</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Bhupendra oli</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:15:42 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9852027449</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:40:19 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:09:56 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Janajagriti Gyan Rashmi Secondary School - Government school P7JV+3QC kharibot station, Banasthhali</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>olibhupendra233@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>CDB287</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>18h 54m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>19h 29m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -634,19 +634,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -750,7 +750,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -764,19 +764,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>3</v>
+      <c r="D6" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -790,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -801,7 +817,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -1768,10 +1784,8 @@
           <t>Bhupendra oli</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9852027449</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9852027449</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1857,10 +1871,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
@@ -1871,29 +1883,29 @@
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>18h 54m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>19h 29m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : blank display  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>18h 54m</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>19h 29m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : blank display  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -1902,6 +1914,218 @@
       <c r="AX5" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:44 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>no light on the router</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379798</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Nabin Bisunkhe</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Nabin Bisunkhe</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9860352861</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:44:59 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9860352861N</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 07:13:50 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11:44:59 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.702764</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Kageshwari Manohara -9, ???????? 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>01:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L39-4</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.374328</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>4h 31m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -852,7 +852,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1984,10 +1984,8 @@
           <t>Nabin Bisunkhe</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9860352861</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9860352861</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2022,10 +2020,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.702764</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.702764</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2077,25 +2073,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L39-4</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.374328</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.37432800000001</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -750,14 +750,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
@@ -766,7 +766,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -780,19 +780,35 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>4</v>
+      <c r="C7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -806,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -819,10 +835,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -852,7 +868,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2121,6 +2137,214 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:32 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : no signal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>no signal</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379231</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Yog Prasad Chaulagain</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Yog Prasad Chaulagain</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9843775048</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:26:05 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>CHB9843775048</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 02:17:56 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:32:20 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>27.71160233052088, 85.30518345816868, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>9843775048@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>08:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB122</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : no signal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>21h 6m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>22h 14m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : no signal   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,14 +528,14 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -546,14 +546,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -562,20 +562,38 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="B5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -590,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -634,19 +652,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -657,19 +675,42 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -684,13 +725,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +743,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -718,17 +765,20 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>1</v>
+      <c r="D2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -741,16 +791,19 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -759,30 +812,36 @@
       <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -791,24 +850,68 @@
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>5</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -822,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -835,10 +938,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -2204,10 +2307,8 @@
           <t>Yog Prasad Chaulagain</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9843775048</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9843775048</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2297,10 +2398,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -2311,35 +2410,1203 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>21h 6m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>22h 14m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : no signal   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>21h 6m</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>22h 14m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:51 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AC8" s="3" t="inlineStr"/>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:48 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>iptv connection</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378231</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Rakchya Nepal</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Rakchya Nepal</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9845431585</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:48:44 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9845431585</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 04:24:55 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:48:44 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Near Ajima Park Details from Google Maps Sahid Basu Smitri Marg, Kirtipur 44618, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>12:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 23m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv connection   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:53 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379068</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Ningwama Kandangwa</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Ningwama Kandangwa</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9823501089</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:05:32 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9823501089</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:05:32 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:53:40 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.712038</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Metropolitan City Office Ward No. 15 - Local government, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>ningwama.op@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>10:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.295641</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>1d 48m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 48m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : no signal   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX7" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:52 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378955</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Pratakshya Dristi Saving &amp; Credit Co- operative Ltd</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Pratakshya Dristi Saving &amp; Credit Co- operative Lt</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9851049287</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:52:02 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9851049287</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:52:02 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:52:26 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Balaju chowk, P8G3+GCQ, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>pratakshya067@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>12:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:51 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378038</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Luis Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Luis Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9843352694</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:12:15 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9843352694</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:12:15 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:51:04 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.73729</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Balaju machhapokhari Bigmart, , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>l.stha65@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>12:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB032</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.29503</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 38m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 38m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:50 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378038</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Luis Shrestha</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Luis Shrestha</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9843352694</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:12:15 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9843352694</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 01:12:15 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 12:51:04 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.73729</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Balaju machhapokhari Bigmart, , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>l.stha65@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>12:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB032</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.29503</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 38m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 38m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2619,10 +2619,8 @@
           <t>Rakchya Nepal</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9845431585</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9845431585</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2708,10 +2706,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2722,7 +2718,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv connection   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2823,10 +2819,8 @@
           <t>Ningwama Kandangwa</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9823501089</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9823501089</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2861,10 +2855,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.712038</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.712038</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2920,25 +2912,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>3,11</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.295641</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.295641</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3039,10 +3027,8 @@
           <t>Pratakshya Dristi Saving &amp; Credit Co- operative Lt</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9851049287</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9851049287</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3132,10 +3118,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -3146,7 +3130,7 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3247,10 +3231,8 @@
           <t>Luis Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9843352694</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9843352694</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3285,10 +3267,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.73729</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.73729</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3344,25 +3324,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB032</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.29503</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.29503</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3463,10 +3439,8 @@
           <t>Luis Shrestha</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9843352694</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9843352694</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3501,10 +3475,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.73729</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.73729</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3560,25 +3532,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>CDB032</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.29503</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.29503</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -769,16 +769,16 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -902,16 +902,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -954,7 +954,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3580,6 +3580,438 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379087</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Center For Quality Surveillance Nepal Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Center For Quality Surveillance Nepal Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9851269123</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:53:56 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9851269123</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:25:35 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:53:56 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.68741</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Department of Foreign Employment, M8QG+2JG, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>cqsnepal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>11:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB037</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.32696</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 28m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 1:42 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378994</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Samjana bhattarai</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Reopen</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Samjana bhattarai</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9843354709</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:45:32 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9865099449</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 11:17:44 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:45:32 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.699446</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki,,near Himshikhar Boarding , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>dahalsamjana086@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.265566</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 27m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (Reopen)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3647,10 +3647,8 @@
           <t>Center For Quality Surveillance Nepal Pvt Ltd</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9851269123</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9851269123</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3685,10 +3683,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.68741</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.68741</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3744,25 +3740,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB037</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.32696</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.32696</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3863,10 +3855,8 @@
           <t>Samjana bhattarai</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9843354709</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9843354709</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3901,10 +3891,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.699446</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.699446</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3942,10 +3930,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH15" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH15" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI15" s="3" t="inlineStr"/>
       <c r="AJ15" s="3" t="inlineStr"/>
@@ -3960,25 +3946,21 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>2,11</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.265566</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.26556600000001</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>3</v>
@@ -911,7 +911,7 @@
         <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3994,6 +3994,214 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 2:40 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379317</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Kushila Upreti</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Kushila Upreti</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9813059309</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:40:34 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9813059309</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:36:18 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:40:34 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Sangam Colony Housing Society Sangam Colony Housing Society - Housing society M7VP+8VC Kathmandu 446</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>jebishbhetwal9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>09:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>23h 4m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -971,7 +971,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4061,10 +4061,8 @@
           <t>Kushila Upreti</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9813059309</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9813059309</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4154,10 +4152,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -4168,7 +4164,7 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -784,17 +784,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>1</v>
@@ -803,17 +803,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -860,14 +860,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -879,14 +879,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -896,22 +896,41 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>13</v>
+      <c r="E10" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -959,7 +978,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -971,7 +990,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4198,6 +4217,222 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 3:15 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : routet not working   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>routet not working</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378218</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Tribikram Shrestha</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Tribikram Shrestha</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9865077101</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:15:16 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9865077101</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 04:09:11 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:15:16 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.7264</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>P8G4+FP6, ?????? ?????, Kathmandu 44600  near by Amrit Secondary Boarding School, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>tribikrabstha567@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>15:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr"/>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L30-1</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.3072</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : routet not working   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 6m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : routet not working   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -990,7 +990,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4284,10 +4284,8 @@
           <t>Tribikram Shrestha</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9865077101</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9865077101</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4322,10 +4320,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.7264</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.7264</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4381,25 +4377,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L30-1</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.3072</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.30719999999999</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : routet not working   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -772,13 +772,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -803,7 +803,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -822,17 +822,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
@@ -841,17 +841,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
@@ -915,22 +915,41 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>14</v>
+      <c r="C11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -990,7 +1009,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4425,6 +4444,426 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 4:14 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB collection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>STB collection</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378248</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Nimesh shrestha</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Nimesh shrestha</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9818251285</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 04:14:03 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9818251285</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 04:41:08 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 04:14:03 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>Device Recovery</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>27.658296501810096,85.34721237820956, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>16:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L42-2</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB collection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 32m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB collection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 4:07 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379083</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Dulal</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Dulal</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9849715976</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 04:07:36 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9849715976</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 12:18:42 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 04:07:36 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.65241</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Imadol Ochu Height surayada school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>frankwankey@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>13:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L33-8</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.34204</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 48m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,72 +528,90 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>72.2%</t>
+      <c r="B6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -652,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -687,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -710,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -725,14 +743,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,20 +762,25 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -769,35 +793,41 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="6" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
-        <v>1</v>
+      <c r="F3" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -807,34 +837,40 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
+      <c r="F4" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -851,9 +887,12 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -864,22 +903,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -891,7 +933,10 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -902,15 +947,18 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -921,15 +969,18 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -940,16 +991,19 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>4</v>
-      </c>
       <c r="D11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <v>16</v>
+      <c r="F11" s="4" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -963,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4511,10 +4565,8 @@
           <t>Nimesh shrestha</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9818251285</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9818251285</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4600,10 +4652,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4614,7 +4664,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : STB collection  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4715,10 +4765,8 @@
           <t>Sujan Dulal</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9849715976</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9849715976</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4753,10 +4801,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.65241</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.65241</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4812,55 +4858,479 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>L33-8</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.34204</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.34204</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 48m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 4:28 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378866</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Padam Nepali</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Padam Nepali</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9860495460</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 04:28:58 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9860495460</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:12:24 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 04:28:58 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.66608</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Near to Boje Pokhari - Pond Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>16:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.35222</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 48m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 16m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX19" s="3" t="inlineStr">
+      <c r="AX20" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : No Internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>No Internet</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379288</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Purba Rani  Waiba</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Purba Rani  Waiba</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9818178727</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 04:24:39 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9818178727</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:11:25 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 04:24:39 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.748993</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Near to Rona International School,Tokha , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>11:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L2-2</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.319808</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : No Internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 13m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : No Internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -1063,7 +1063,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -4973,10 +4973,8 @@
           <t>Padam Nepali</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9860495460</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9860495460</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -5011,10 +5009,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.66608</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.66608</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -5066,25 +5062,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.35222</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.35222</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -5185,10 +5177,8 @@
           <t>Purba Rani  Waiba</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9818178727</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9818178727</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5223,10 +5213,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.748993</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.748993</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5260,10 +5248,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH21" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH21" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
@@ -5282,25 +5268,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>L2-2</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.319808</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.31980799999999</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : No Internet   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX21"/>
+  <dimension ref="A1:AX22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1063,7 +1063,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5316,6 +5316,218 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 4:54 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378866</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Padam Nepali</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Padam Nepali</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9860495460</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 04:39:34 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9860495460</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 10:12:24 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:00:06 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.66608</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Near to Boje Pokhari - Pond Mahalaxmi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>16:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.35222</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>20m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 47m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -805,7 +805,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>6</v>
@@ -1003,7 +1003,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX22"/>
+  <dimension ref="A1:AX23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5383,10 +5383,8 @@
           <t>Padam Nepali</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9860495460</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9860495460</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5421,10 +5419,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.66608</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.66608</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5476,47 +5472,43 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.35222</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.35222</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>20m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 47m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
           <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>20m</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>1d 6h 47m</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -5525,6 +5517,222 @@
       <c r="AX22" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 5:10 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380307</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Ghimiri</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Ghimiri</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9813271363</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:10:11 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9813271363S</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:54:56 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:10:11 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.722129</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Boudha dharatole, Kathmandu 44600 AT Burger, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>cargoado265@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>03:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Hareram Pandit</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>L47-6</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.360628</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>3h 15m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>79.2%</t>
         </is>
       </c>
     </row>
@@ -670,19 +670,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -811,42 +811,42 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>2</v>
@@ -877,20 +877,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Welcome Screen Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>1</v>
@@ -899,20 +899,20 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>1</v>
@@ -921,7 +921,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -943,7 +943,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -965,7 +965,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Setup Box Recovery</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -985,25 +985,47 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Setup Box Recovery</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>19</v>
+      <c r="F12" s="4" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX23"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5577,20 +5599,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="3" t="inlineStr">
         <is>
           <t>Sudip Ghimiri</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9813271363</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9813271363</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5625,10 +5641,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.722129</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.722129</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5684,55 +5698,487 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>L47-6</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.360628</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.36062800000001</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>3h 15m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 5:21 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>slow internet issue</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1378180</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Shisir Bhushal</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Shisir Bhushal</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9851170422</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:21:03 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9851170422</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>25 Oct 2026 03:22:25 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:21:03 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.72079</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>27.69506,85.34265, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>bshisir3@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>17:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Abina Chitrakar</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.28102</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>3h 15m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 58m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW23" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX23" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 5:18 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380259</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Suman Rai</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Suman Rai</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9801167083</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:18:12 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9861371128</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:24:51 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05:18:12 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.72706</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>27.73722, 85.37458, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>raisumano863@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>03:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.3691</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>3h 53m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_27_Oct_2026.xlsx
@@ -1085,7 +1085,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -5813,10 +5813,8 @@
           <t>Shisir Bhushal</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9851170422</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9851170422</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5851,10 +5849,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.72079</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.72079</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5910,25 +5906,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>4,10</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.28102</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.28102</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -6029,10 +6021,8 @@
           <t>Suman Rai</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9801167083</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9801167083</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6067,10 +6057,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.72706</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.72706</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -6108,10 +6096,8 @@
           <t>Router Upgrade Dual Band</t>
         </is>
       </c>
-      <c r="AH25" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH25" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
@@ -6130,25 +6116,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>3,8</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.3691</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.3691</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
